--- a/database/excels/reference/base-seeder.xlsx
+++ b/database/excels/reference/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDC2538-995C-3A45-842B-DE2ADE195E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AA10C1-F67D-AF4D-B289-023A3136475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -428,24 +428,6 @@
     <t>table_chart</t>
   </si>
   <si>
-    <t>reference-echelonroom</t>
-  </si>
-  <si>
-    <t>echelon</t>
-  </si>
-  <si>
-    <t>echelon/:echelon/room</t>
-  </si>
-  <si>
-    <t>reference-sectionroom</t>
-  </si>
-  <si>
-    <t>section</t>
-  </si>
-  <si>
-    <t>section/:section/room</t>
-  </si>
-  <si>
     <t>reference-bloodtype</t>
   </si>
   <si>
@@ -456,6 +438,24 @@
   </si>
   <si>
     <t>worktype/:worktype/workunit</t>
+  </si>
+  <si>
+    <t>reference-echelonmap</t>
+  </si>
+  <si>
+    <t>echelonmap</t>
+  </si>
+  <si>
+    <t>echelonmap/:echelonmap/echelon</t>
+  </si>
+  <si>
+    <t>reference-sectionmap</t>
+  </si>
+  <si>
+    <t>sectionmap</t>
+  </si>
+  <si>
+    <t>sectionmap/:sectionmap/section</t>
   </si>
 </sst>
 </file>
@@ -992,7 +992,7 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
         <v>106</v>
@@ -1001,13 +1001,13 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -1018,7 +1018,7 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
         <v>107</v>
@@ -1027,7 +1027,7 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G5" s="4" t="b">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1073,7 +1073,7 @@
         <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
         <v>109</v>
@@ -1082,7 +1082,7 @@
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G7" s="4" t="b">
         <v>1</v>
@@ -1099,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>110</v>
@@ -1108,7 +1108,7 @@
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G8" s="4" t="b">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
@@ -1290,7 +1290,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
         <v>117</v>
@@ -1299,7 +1299,7 @@
         <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G15" s="4" t="b">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G16" s="4" t="b">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1791,7 +1791,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -1802,7 +1802,7 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -1824,7 +1824,7 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -1835,7 +1835,7 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
@@ -1846,7 +1846,7 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -1912,7 +1912,7 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -2187,7 +2187,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2198,7 +2198,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2220,7 +2220,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2231,7 +2231,7 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2242,7 +2242,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2308,7 +2308,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2551,7 +2551,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
@@ -2565,7 +2565,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2593,7 +2593,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -2607,7 +2607,7 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -2621,7 +2621,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -2705,7 +2705,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>

--- a/database/excels/reference/base-seeder.xlsx
+++ b/database/excels/reference/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7AA10C1-F67D-AF4D-B289-023A3136475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1260A216-24FC-2049-80C6-7341009B84F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="5" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="143">
   <si>
     <t>name</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>sectionmap/:sectionmap/section</t>
+  </si>
+  <si>
+    <t>title</t>
   </si>
 </sst>
 </file>
@@ -891,19 +894,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.83203125" style="4"/>
-    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.83203125" style="4"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -911,54 +915,57 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
       <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="b">
+      <c r="H2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -966,25 +973,28 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>105</v>
       </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="4" t="b">
+      <c r="H3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I3" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -992,25 +1002,28 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
         <v>136</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>106</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="4" t="b">
+      <c r="H4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1018,28 +1031,31 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
         <v>75</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>107</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>138</v>
       </c>
-      <c r="G5" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1047,25 +1063,28 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
         <v>60</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>108</v>
       </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="4" t="b">
+      <c r="H6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I6" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1073,25 +1092,28 @@
         <v>35</v>
       </c>
       <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
         <v>139</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>109</v>
       </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
       <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
         <v>140</v>
       </c>
-      <c r="G7" s="4" t="b">
+      <c r="H7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I7" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1099,28 +1121,31 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
         <v>76</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>110</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H8" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1128,25 +1153,28 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
         <v>132</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>111</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
       <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
         <v>111</v>
       </c>
-      <c r="G9" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1154,25 +1182,28 @@
         <v>38</v>
       </c>
       <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
         <v>61</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>112</v>
       </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
       <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1180,28 +1211,31 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
         <v>78</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>113</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
       <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1209,25 +1243,28 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>114</v>
       </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
       <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1235,28 +1272,31 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
         <v>77</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>115</v>
       </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
       <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H13" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1264,25 +1304,28 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
         <v>63</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>116</v>
       </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
       <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1290,25 +1333,28 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
         <v>133</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>117</v>
       </c>
-      <c r="E15" t="s">
-        <v>25</v>
-      </c>
       <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
         <v>134</v>
       </c>
-      <c r="G15" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1316,28 +1362,31 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
         <v>79</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>118</v>
       </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
       <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
         <v>135</v>
       </c>
-      <c r="G16" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H16" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1345,25 +1394,28 @@
         <v>46</v>
       </c>
       <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
         <v>64</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>119</v>
       </c>
-      <c r="E17" t="s">
-        <v>25</v>
-      </c>
       <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
         <v>90</v>
       </c>
-      <c r="G17" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H17" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1371,28 +1423,31 @@
         <v>47</v>
       </c>
       <c r="C18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>119</v>
       </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
       <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
         <v>91</v>
       </c>
-      <c r="G18" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H18" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1400,28 +1455,31 @@
         <v>48</v>
       </c>
       <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
         <v>81</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>119</v>
       </c>
-      <c r="E19" t="s">
-        <v>25</v>
-      </c>
       <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
         <v>92</v>
       </c>
-      <c r="G19" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H19" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1429,28 +1487,31 @@
         <v>49</v>
       </c>
       <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
         <v>82</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>119</v>
       </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
       <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H20" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1458,25 +1519,28 @@
         <v>50</v>
       </c>
       <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
         <v>65</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>120</v>
       </c>
-      <c r="E21" t="s">
-        <v>25</v>
-      </c>
       <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1484,28 +1548,31 @@
         <v>51</v>
       </c>
       <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
         <v>83</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>121</v>
       </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
       <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
         <v>95</v>
       </c>
-      <c r="G22" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H22" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1513,25 +1580,28 @@
         <v>53</v>
       </c>
       <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>122</v>
       </c>
-      <c r="E23" t="s">
-        <v>25</v>
-      </c>
       <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H23" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1539,25 +1609,28 @@
         <v>54</v>
       </c>
       <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
         <v>67</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>128</v>
       </c>
-      <c r="E24" t="s">
-        <v>25</v>
-      </c>
       <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
         <v>97</v>
       </c>
-      <c r="G24" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1565,25 +1638,28 @@
         <v>52</v>
       </c>
       <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
         <v>68</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>129</v>
       </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
       <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
         <v>98</v>
       </c>
-      <c r="G25" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H25" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1591,25 +1667,28 @@
         <v>45</v>
       </c>
       <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
         <v>69</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>123</v>
       </c>
-      <c r="E26" t="s">
-        <v>25</v>
-      </c>
       <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1617,25 +1696,28 @@
         <v>55</v>
       </c>
       <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
         <v>70</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>124</v>
       </c>
-      <c r="E27" t="s">
-        <v>25</v>
-      </c>
       <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
         <v>100</v>
       </c>
-      <c r="G27" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1643,25 +1725,28 @@
         <v>56</v>
       </c>
       <c r="C28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" t="s">
         <v>71</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>130</v>
       </c>
-      <c r="E28" t="s">
-        <v>25</v>
-      </c>
       <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
         <v>101</v>
       </c>
-      <c r="G28" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H28" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -1669,25 +1754,28 @@
         <v>57</v>
       </c>
       <c r="C29" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" t="s">
         <v>72</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>131</v>
       </c>
-      <c r="E29" t="s">
-        <v>25</v>
-      </c>
       <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H29" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1695,25 +1783,28 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>125</v>
       </c>
-      <c r="E30" t="s">
-        <v>25</v>
-      </c>
       <c r="F30" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" t="s">
         <v>103</v>
       </c>
-      <c r="G30" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -1721,21 +1812,24 @@
         <v>59</v>
       </c>
       <c r="C31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" t="s">
         <v>74</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>126</v>
       </c>
-      <c r="E31" t="s">
-        <v>25</v>
-      </c>
       <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" t="s">
         <v>104</v>
       </c>
-      <c r="G31" s="4" t="b">
-        <v>0</v>
-      </c>
       <c r="H31" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="b">
         <v>1</v>
       </c>
     </row>
